--- a/artfynd/A 32640-2022 artfynd.xlsx
+++ b/artfynd/A 32640-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32640-2022 artfynd.xlsx
+++ b/artfynd/A 32640-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2152938</v>
+        <v>103711638</v>
       </c>
       <c r="B2" t="n">
-        <v>107996</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>2590</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Idegransreservatet, Öl</t>
+          <t>S om Idegransreservatet, Öl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619903.3766831954</v>
+        <v>619889</v>
       </c>
       <c r="R2" t="n">
-        <v>6346850.193946955</v>
+        <v>6346803</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-05-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-05-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +758,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103711638</v>
+        <v>2152938</v>
       </c>
       <c r="B3" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,35 +784,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2590</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S om Idegransreservatet, Öl</t>
+          <t>Idegransreservatet, Öl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619889.018100369</v>
+        <v>619903</v>
       </c>
       <c r="R3" t="n">
-        <v>6346803.221470654</v>
+        <v>6346850</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,30 +855,34 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
+          <t>Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pontus Axén</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Thomas Gunnarsson, Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>112088271</v>
       </c>
       <c r="B4" t="n">
-        <v>98935</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32640-2022 artfynd.xlsx
+++ b/artfynd/A 32640-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103711638</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2152938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,8 +989,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112088271</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>